--- a/artfynd/A 58654-2023 artfynd.xlsx
+++ b/artfynd/A 58654-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 58654-2023 artfynd.xlsx
+++ b/artfynd/A 58654-2023 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>106032012</v>
+        <v>106032013</v>
       </c>
       <c r="B2" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92147</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>1101</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>561226.5593844455</v>
+        <v>561289</v>
       </c>
       <c r="R2" t="n">
-        <v>6599751.974692489</v>
+        <v>6599796</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,21 +743,11 @@
           <t>2022-08-03</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-08-03</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -772,7 +757,36 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AT2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Äldre barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Rötbruten granstubbe # Picea abies</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
       <c r="AW2" t="inlineStr">
         <is>
           <t>Jacob Rudhe</t>
@@ -787,15 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>106032016</v>
+        <v>106032014</v>
       </c>
       <c r="B3" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -827,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>561319.776654334</v>
+        <v>561275</v>
       </c>
       <c r="R3" t="n">
-        <v>6599801.183273373</v>
+        <v>6599775</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,19 +869,9 @@
           <t>2022-08-03</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-08-03</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,15 +918,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>106032013</v>
+        <v>106032016</v>
       </c>
       <c r="B4" t="n">
-        <v>89608</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -935,21 +929,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1101</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -959,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>561288.8668210321</v>
+        <v>561320</v>
       </c>
       <c r="R4" t="n">
-        <v>6599795.605938765</v>
+        <v>6599801</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,21 +986,11 @@
           <t>2022-08-03</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-08-03</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1033,19 +1017,10 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Rötbruten granstubbe # Picea abies</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>Tom Sävström</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
+          <t>Granlåga # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
           <t>Jacob Rudhe</t>
@@ -1060,37 +1035,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>106032021</v>
+        <v>106032017</v>
       </c>
       <c r="B5" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1100,10 +1070,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>561354.0334945008</v>
+        <v>561296</v>
       </c>
       <c r="R5" t="n">
-        <v>6599632.797432769</v>
+        <v>6599967</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1133,21 +1103,11 @@
           <t>2022-08-03</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-08-03</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1160,6 +1120,21 @@
       <c r="AI5" t="inlineStr">
         <is>
           <t>Äldre barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1177,15 +1152,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>106032020</v>
+        <v>106032019</v>
       </c>
       <c r="B6" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,10 +1187,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>561323.8344184794</v>
+        <v>561357</v>
       </c>
       <c r="R6" t="n">
-        <v>6599739.354675747</v>
+        <v>6599775</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1250,19 +1220,9 @@
           <t>2022-08-03</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-08-03</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1309,15 +1269,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>106032017</v>
+        <v>106032020</v>
       </c>
       <c r="B7" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,10 +1304,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>561295.7333648218</v>
+        <v>561324</v>
       </c>
       <c r="R7" t="n">
-        <v>6599966.684473055</v>
+        <v>6599739</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1382,19 +1337,9 @@
           <t>2022-08-03</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-08-03</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1441,37 +1386,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>106032014</v>
+        <v>106032012</v>
       </c>
       <c r="B8" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>2180</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1481,10 +1421,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>561274.9631236023</v>
+        <v>561226</v>
       </c>
       <c r="R8" t="n">
-        <v>6599775.593353357</v>
+        <v>6599752</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1514,21 +1454,11 @@
           <t>2022-08-03</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-08-03</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1537,26 +1467,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Äldre barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Granlåga # Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1573,37 +1483,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>106032019</v>
+        <v>106032021</v>
       </c>
       <c r="B9" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>2180</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1613,10 +1518,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>561357.3130525054</v>
+        <v>561354</v>
       </c>
       <c r="R9" t="n">
-        <v>6599774.399769727</v>
+        <v>6599633</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1646,21 +1551,11 @@
           <t>2022-08-03</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-08-03</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1673,21 +1568,6 @@
       <c r="AI9" t="inlineStr">
         <is>
           <t>Äldre barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1708,12 +1588,7 @@
         <v>106032018</v>
       </c>
       <c r="B10" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 58654-2023 artfynd.xlsx
+++ b/artfynd/A 58654-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -798,6 +803,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106032013</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -915,6 +925,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106032014</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1032,6 +1047,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106032016</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1149,6 +1169,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106032017</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1266,6 +1291,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106032019</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1383,6 +1413,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106032020</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1480,6 +1515,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106032012</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1582,6 +1622,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106032021</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1704,8 +1749,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106032018</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>